--- a/teachers.xlsx
+++ b/teachers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="130">
   <si>
     <t>ΑΡΓΥΡΟΠΟΥΛΟΥ</t>
   </si>
@@ -34,9 +34,6 @@
     <t>ΝΙΚΗΤΑ</t>
   </si>
   <si>
-    <t>ΠΑΠΑΙΩΑΝΝΟΥ</t>
-  </si>
-  <si>
     <t>ΡΩΜΑΝΑ</t>
   </si>
   <si>
@@ -46,15 +43,6 @@
     <t>ΣΙΔΕΡΗ</t>
   </si>
   <si>
-    <t>ΣΚΙΚΟΥ</t>
-  </si>
-  <si>
-    <t>ΣΤΑΜΑΤΑΚΗ</t>
-  </si>
-  <si>
-    <t>ΣΤΑΜΟΥ</t>
-  </si>
-  <si>
     <t>ΕΛΙΣΑΒΕΤ</t>
   </si>
   <si>
@@ -70,12 +58,6 @@
     <t>ΕΜΜΑΝΟΥΗΛ</t>
   </si>
   <si>
-    <t>ΙΩΑΝΝΑ</t>
-  </si>
-  <si>
-    <t>ΔΗΜΗΤΡΙΟΣ</t>
-  </si>
-  <si>
     <t>ΠΑΡΑΣΚΕΥΗ</t>
   </si>
   <si>
@@ -88,15 +70,6 @@
     <t>ΧΡΙΣΤΙΝΑ</t>
   </si>
   <si>
-    <t>ΣΠΥΡΙΔΟΥΛΑ</t>
-  </si>
-  <si>
-    <t>ΣΤΥΛΙΑΝΗ</t>
-  </si>
-  <si>
-    <t>ΜΑΡΙΝΑ</t>
-  </si>
-  <si>
     <t>argirolisab@gmail.com</t>
   </si>
   <si>
@@ -106,9 +79,6 @@
     <t>zervouaikaterini1966@gmail.com</t>
   </si>
   <si>
-    <t>thanasiselias@yahoo.gr</t>
-  </si>
-  <si>
     <t>vkalaitzis@hotmail.com</t>
   </si>
   <si>
@@ -118,21 +88,12 @@
     <t>nikloudar@sch.gr</t>
   </si>
   <si>
-    <t>gianman4@gmail.com</t>
-  </si>
-  <si>
     <t>bozionel@sch.gr</t>
   </si>
   <si>
     <t>emoraitis@sch.gr</t>
   </si>
   <si>
-    <t>ioannanikita17@gmail.com</t>
-  </si>
-  <si>
-    <t>argospap1@gmail.com</t>
-  </si>
-  <si>
     <t>pantelis.roumeliotis@gmail.com</t>
   </si>
   <si>
@@ -145,18 +106,9 @@
     <t>csideri1@gmail.com</t>
   </si>
   <si>
-    <t>g.mpast@yahoo.com</t>
-  </si>
-  <si>
     <t>stfanis@gmail.com</t>
   </si>
   <si>
-    <t>stellastamataki63@gmail.com</t>
-  </si>
-  <si>
-    <t>sta71mouma@gmail.com</t>
-  </si>
-  <si>
     <t>gtassias@gmail.com</t>
   </si>
   <si>
@@ -166,9 +118,6 @@
     <t>ΦΙΛΗ</t>
   </si>
   <si>
-    <t>ΧΡΟΝΟΠΟΥΛΟΣ</t>
-  </si>
-  <si>
     <t>ΜΑΓΔΑΛΗΝΗ</t>
   </si>
   <si>
@@ -196,9 +145,6 @@
     <t>ΠΕ79</t>
   </si>
   <si>
-    <t>ΠΕ11</t>
-  </si>
-  <si>
     <t>ΠΕ01</t>
   </si>
   <si>
@@ -235,9 +181,6 @@
     <t>ΖΕΡΒΟΥ ΑΙΚΑΤΕΡΙΝΗ</t>
   </si>
   <si>
-    <t>ΗΛΙΑΣ ΑΘΑΝΑΣΙΟΣ</t>
-  </si>
-  <si>
     <t>ΚΑΛΑΪΤΖΗΣ ΕΥΑΓΓΕΛΟΣ</t>
   </si>
   <si>
@@ -247,21 +190,12 @@
     <t>ΛΟΥΔΑΡΟΣ ΝΙΚΗΤΑΣ</t>
   </si>
   <si>
-    <t>ΜΑΝΩΛΗΣ ΙΩΑΝΝΝΗΣ</t>
-  </si>
-  <si>
     <t>ΜΠΟΖΙΟΝΕΛΟΥ ΔΗΜΗΤΡΑ</t>
   </si>
   <si>
     <t>ΜΩΡΑΪΤΗΣ ΕΜΜΑΝΟΥΗΛ</t>
   </si>
   <si>
-    <t>ΝΙΚΗΤΑ ΙΩΑΝΝΑ</t>
-  </si>
-  <si>
-    <t>ΠΑΠΑΪΩΑΝΝΟΥ ΔΗΜΗΤΡΙΟΣ</t>
-  </si>
-  <si>
     <t>ΡΟΥΜΕΛΙΩΤΗΣ ΠΑΝΤΕΛΕΗΜΩΝ</t>
   </si>
   <si>
@@ -274,33 +208,18 @@
     <t>ΣΙΔΕΡΗ ΧΡΙΣΤΙΝΑ</t>
   </si>
   <si>
-    <t>ΣΚΙΚΟΥ ΣΠΥΡΙΔΟΥΛΑ</t>
-  </si>
-  <si>
     <t>ΣΤΑΘΟΠΟΥΛΟΣ ΘΕΟΦΑΝΗΣ</t>
   </si>
   <si>
-    <t>ΣΤΑΜΑΤΑΚΗ ΣΤΥΛΙΑΝΗ</t>
-  </si>
-  <si>
-    <t>ΣΤΑΜΟΥ ΜΑΡΙΝΑ</t>
-  </si>
-  <si>
     <t>ΤΑΣΣΙΑΣ ΓΕΩΡΓΙΟΣ</t>
   </si>
   <si>
     <t>ΝΙΚΟΛΑΟ</t>
   </si>
   <si>
-    <t>ΑΘΑΝΑΣΙΟ</t>
-  </si>
-  <si>
     <t>ΕΥΑΓΓΕΛΟ</t>
   </si>
   <si>
-    <t>ΙΩΑΝΝΗ</t>
-  </si>
-  <si>
     <t>ΔΗΜΗΤΡΙΟ</t>
   </si>
   <si>
@@ -319,18 +238,12 @@
     <t>ΤΑΣΣΙΑ</t>
   </si>
   <si>
-    <t>ΗΛΙΑ</t>
-  </si>
-  <si>
     <t>ΚΑΛΑΪΤΖΗ</t>
   </si>
   <si>
     <t>ΛΟΥΔΑΡΟ</t>
   </si>
   <si>
-    <t>ΜΑΝΩΛΗ</t>
-  </si>
-  <si>
     <t>ΜΩΡΑΪΤΗ</t>
   </si>
   <si>
@@ -361,18 +274,12 @@
     <t>171505</t>
   </si>
   <si>
-    <t>208164</t>
-  </si>
-  <si>
     <t>195034</t>
   </si>
   <si>
     <t>156161</t>
   </si>
   <si>
-    <t>188113</t>
-  </si>
-  <si>
     <t>188141</t>
   </si>
   <si>
@@ -385,18 +292,9 @@
     <t>201955</t>
   </si>
   <si>
-    <t>185476</t>
-  </si>
-  <si>
     <t>205773</t>
   </si>
   <si>
-    <t>177013</t>
-  </si>
-  <si>
-    <t>197494</t>
-  </si>
-  <si>
     <t>179779</t>
   </si>
   <si>
@@ -416,13 +314,103 @@
   </si>
   <si>
     <t>mitrwo</t>
+  </si>
+  <si>
+    <t>ΜΥΛΩΝΑ</t>
+  </si>
+  <si>
+    <t>ΜΥΛΩΝΑΣ ΛΑΜΠΡΟΣ</t>
+  </si>
+  <si>
+    <t>ΛΑΜΠΡΟ</t>
+  </si>
+  <si>
+    <t>ΠΑΠΑΔΟΠΟΥΛΟΣ ΚΩΝΣΤΑΝΤΙΝΟΣ</t>
+  </si>
+  <si>
+    <t>ΠΑΠΑΔΟΠΟΥΛΟ</t>
+  </si>
+  <si>
+    <t>ΚΩΝΣΤΑΝΤΝΟ</t>
+  </si>
+  <si>
+    <t>guspapad@yahoo.gr</t>
+  </si>
+  <si>
+    <t>lamprosmyl@gmail.com</t>
+  </si>
+  <si>
+    <t>ΧΡΟΝΟΠΟΥΛΟ</t>
+  </si>
+  <si>
+    <t>eponymo_gen</t>
+  </si>
+  <si>
+    <t>onoma_gen</t>
+  </si>
+  <si>
+    <t>ΛΟΥΔΑΡΟΥ</t>
+  </si>
+  <si>
+    <t>ΠΑΠΑΔΟΠΟΥΛΟΥ</t>
+  </si>
+  <si>
+    <t>ΣΤΑΘΟΠΟΥΛΟΥ</t>
+  </si>
+  <si>
+    <t>ΧΡΟΝΟΠΟΥΛΟΥ</t>
+  </si>
+  <si>
+    <t>ΝΙΚΟΛΑΟΥ</t>
+  </si>
+  <si>
+    <t>ΑΙΚΑΤΕΡΙΝΗΣ</t>
+  </si>
+  <si>
+    <t>ΕΥΑΓΓΕΛΟΥ</t>
+  </si>
+  <si>
+    <t>ΚΥΡΙΑΚΟΥΛΑΣ</t>
+  </si>
+  <si>
+    <t>ΔΗΜΗΤΡΑΣ</t>
+  </si>
+  <si>
+    <t>ΛΑΜΠΡΟΥ</t>
+  </si>
+  <si>
+    <t>ΚΩΝΣΤΑΝΤΝΟΥ</t>
+  </si>
+  <si>
+    <t>ΠΑΝΤΕΛΕΗΜΟΝΟΣ</t>
+  </si>
+  <si>
+    <t>ΕΛΕΝΗΣ</t>
+  </si>
+  <si>
+    <t>ΔΕΣΠΟΙΝΑΣ</t>
+  </si>
+  <si>
+    <t>ΧΡΙΣΤΙΝΑΣ</t>
+  </si>
+  <si>
+    <t>ΓΕΩΡΓΙΟΥ</t>
+  </si>
+  <si>
+    <t>ΜΑΓΔΑΛΗΝΗΣ</t>
+  </si>
+  <si>
+    <t>ΠΑΡΑΣΚΕΥΗΣ</t>
+  </si>
+  <si>
+    <t>ΔΗΜΗΤΡΙΟΥ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -444,6 +432,35 @@
       <color theme="10"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF666666"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="161"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="161"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="161"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="161"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -463,7 +480,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -486,19 +503,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -507,7 +511,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -519,15 +523,22 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
@@ -823,518 +834,543 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.42578125" customWidth="1"/>
     <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="35.42578125" customWidth="1"/>
-    <col min="7" max="7" width="6.5703125" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" customWidth="1"/>
+    <col min="3" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="35.42578125" customWidth="1"/>
+    <col min="9" max="9" width="6.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C1" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D1" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="E1" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="F1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="14.25" customHeight="1">
+        <v>50</v>
+      </c>
+      <c r="G1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="14.25" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="14.25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="14.25" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" customHeight="1">
+        <v>66</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="B7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15" customHeight="1">
+      <c r="A9" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="B9" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="D9" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="8">
+        <v>730624</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A9" s="1" t="s">
+      <c r="E11" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="8">
+        <v>219657</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="C12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A13" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A12" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A13" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="H19" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="15" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="G20" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A16" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A17" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15" customHeight="1">
-      <c r="A18" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A19" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A20" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A21" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A22" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>54</v>
+      <c r="H20" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F23" r:id="rId1"/>
+    <hyperlink ref="H18" r:id="rId1"/>
+    <hyperlink ref="H9" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.39" right="0.39" top="0.39" bottom="0.39" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId3"/>
 </worksheet>
 </file>
--- a/teachers.xlsx
+++ b/teachers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="135">
   <si>
     <t>ΑΡΓΥΡΟΠΟΥΛΟΥ</t>
   </si>
@@ -331,9 +331,6 @@
     <t>ΠΑΠΑΔΟΠΟΥΛΟ</t>
   </si>
   <si>
-    <t>ΚΩΝΣΤΑΝΤΝΟ</t>
-  </si>
-  <si>
     <t>guspapad@yahoo.gr</t>
   </si>
   <si>
@@ -404,6 +401,24 @@
   </si>
   <si>
     <t>ΔΗΜΗΤΡΙΟΥ</t>
+  </si>
+  <si>
+    <t>ΚΩΝΣΤΑΝΤΙΝΟ</t>
+  </si>
+  <si>
+    <t>ΦΙΛΗ ΑΝΝΑ</t>
+  </si>
+  <si>
+    <t>ΑΝΝΑ</t>
+  </si>
+  <si>
+    <t>ΑΝΝΑΣ</t>
+  </si>
+  <si>
+    <t>ΠΕ11</t>
+  </si>
+  <si>
+    <t>filiannoula@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -834,7 +849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.42578125" customWidth="1"/>
@@ -856,10 +871,10 @@
         <v>49</v>
       </c>
       <c r="D1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" t="s">
         <v>109</v>
-      </c>
-      <c r="E1" t="s">
-        <v>110</v>
       </c>
       <c r="F1" t="s">
         <v>50</v>
@@ -911,7 +926,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>39</v>
@@ -937,7 +952,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>40</v>
@@ -963,7 +978,7 @@
         <v>74</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>41</v>
@@ -989,7 +1004,7 @@
         <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>40</v>
@@ -1012,7 +1027,7 @@
         <v>5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>5</v>
@@ -1041,7 +1056,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>43</v>
@@ -1067,7 +1082,7 @@
         <v>100</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>38</v>
@@ -1076,7 +1091,7 @@
         <v>730624</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1">
@@ -1113,13 +1128,13 @@
         <v>104</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>46</v>
@@ -1128,7 +1143,7 @@
         <v>219657</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -1145,7 +1160,7 @@
         <v>77</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>44</v>
@@ -1171,7 +1186,7 @@
         <v>6</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>41</v>
@@ -1197,7 +1212,7 @@
         <v>7</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>45</v>
@@ -1223,7 +1238,7 @@
         <v>8</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>40</v>
@@ -1246,7 +1261,7 @@
         <v>70</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>70</v>
@@ -1275,7 +1290,7 @@
         <v>73</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>40</v>
@@ -1301,7 +1316,7 @@
         <v>32</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>40</v>
@@ -1315,53 +1330,79 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G19" s="8">
+        <v>702963</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="F20" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G21" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>37</v>
       </c>
     </row>
